--- a/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497653333968</v>
+        <v>10.84497613320512</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907264272365</v>
+        <v>37.78907124846393</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.471680866394974</v>
+        <v>6.013204688511713</v>
       </c>
       <c r="C2" t="n">
-        <v>7.937430188835462</v>
+        <v>6.110397711232148</v>
       </c>
       <c r="D2" t="n">
-        <v>21.79283553887069</v>
+        <v>31.33935021496668</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.76887268334127</v>
+        <v>18.03470532701391</v>
       </c>
       <c r="C3" t="n">
-        <v>24.59768872990384</v>
+        <v>27.86690858504571</v>
       </c>
       <c r="D3" t="n">
-        <v>70.59256867386691</v>
+        <v>70.66619975168541</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.18904500522568</v>
+        <v>38.41578766717769</v>
       </c>
       <c r="C4" t="n">
-        <v>74.176929542072</v>
+        <v>59.33388600156448</v>
       </c>
       <c r="D4" t="n">
-        <v>92.91260272991813</v>
+        <v>82.28125684062942</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.66447293598841</v>
+        <v>48.27744335633691</v>
       </c>
       <c r="C5" t="n">
-        <v>104.65430527271</v>
+        <v>86.39379797371933</v>
       </c>
       <c r="D5" t="n">
-        <v>69.80226177194822</v>
+        <v>59.8375225738431</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.43782808502763</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>95.19516614229198</v>
+        <v>86.29955019411163</v>
       </c>
       <c r="D6" t="n">
-        <v>47.69821221083129</v>
+        <v>43.39128503230054</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="C7" t="n">
-        <v>81.02658327460199</v>
+        <v>75.51701515836889</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>53.7408693304704</v>
+        <v>55.66018609227291</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.70375402019938</v>
+        <v>7.724771888788264</v>
       </c>
       <c r="C21" t="n">
-        <v>95.33395599996734</v>
+        <v>96.5596486098533</v>
       </c>
       <c r="D21" t="n">
-        <v>8.666723272724303</v>
+        <v>8.690368374886797</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.659595588533614</v>
+        <v>7.747952881915827</v>
       </c>
       <c r="C2" t="n">
-        <v>14.64473050424967</v>
+        <v>5.932701376763475</v>
       </c>
       <c r="D2" t="n">
-        <v>17.17174909498096</v>
+        <v>23.89966611218435</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.13211933391259</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="C3" t="n">
-        <v>27.75891633757857</v>
+        <v>25.54998400302324</v>
       </c>
       <c r="D3" t="n">
-        <v>71.06380757190537</v>
+        <v>78.19129590473722</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.03214529899544</v>
+        <v>36.15678619970578</v>
       </c>
       <c r="C4" t="n">
-        <v>67.61689138229482</v>
+        <v>64.06885517914685</v>
       </c>
       <c r="D4" t="n">
-        <v>103.9778811044839</v>
+        <v>97.30297846330987</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.65313393189395</v>
+        <v>52.7443954106599</v>
       </c>
       <c r="C5" t="n">
-        <v>119.3314334511998</v>
+        <v>98.1502267320749</v>
       </c>
       <c r="D5" t="n">
-        <v>85.43659396207869</v>
+        <v>73.48381566287377</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.75483478250812</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>129.4493252911675</v>
+        <v>111.4568351154361</v>
       </c>
       <c r="D6" t="n">
-        <v>56.83533809425636</v>
+        <v>51.72337779824321</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.20198765183014</v>
+        <v>39.88448223273092</v>
       </c>
       <c r="C7" t="n">
-        <v>107.4964648765045</v>
+        <v>99.05245287227768</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.11663235482289</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="C8" t="n">
-        <v>79.77681844709581</v>
+        <v>77.94095024015427</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>50.14374574211007</v>
+        <v>51.9187455913883</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.58482819875739</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.888158513664123</v>
+        <v>7.915040634321652</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5181003060496</v>
+        <v>105.8636684840521</v>
       </c>
       <c r="D21" t="n">
-        <v>9.860198142080154</v>
+        <v>9.893800792902065</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.969647936626359</v>
+        <v>10.11789183996763</v>
       </c>
       <c r="C2" t="n">
-        <v>11.64156427695868</v>
+        <v>5.497787143782138</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47591095684822</v>
+        <v>24.20302615279661</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.92871763268426</v>
+        <v>22.28076414788136</v>
       </c>
       <c r="C3" t="n">
-        <v>41.92062697133881</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="D3" t="n">
-        <v>68.29527904592936</v>
+        <v>78.3483755374167</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.27914480983814</v>
+        <v>35.92705723691203</v>
       </c>
       <c r="C4" t="n">
-        <v>67.56584050167397</v>
+        <v>63.20099020859267</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2180904968549</v>
+        <v>109.6828170138621</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.95394964002097</v>
+        <v>53.79977419272522</v>
       </c>
       <c r="C5" t="n">
-        <v>120.3131811554466</v>
+        <v>107.4031988446011</v>
       </c>
       <c r="D5" t="n">
-        <v>98.49383842856128</v>
+        <v>88.70090507869934</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.52969576306612</v>
+        <v>61.38377520803183</v>
       </c>
       <c r="C6" t="n">
-        <v>156.2166764474567</v>
+        <v>130.6971266232651</v>
       </c>
       <c r="D6" t="n">
-        <v>68.06555008313562</v>
+        <v>60.41773546705297</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.4007837141735</v>
+        <v>50.54429880544279</v>
       </c>
       <c r="C7" t="n">
-        <v>141.3922861133299</v>
+        <v>127.7980256526243</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.96217917008666</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="C8" t="n">
-        <v>107.0644958866359</v>
+        <v>101.8072369303942</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C9" t="n">
-        <v>71.99843138634832</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.057112446451111</v>
+        <v>8.090609863117125</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7995742503156</v>
+        <v>114.2798643165294</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07852961387028</v>
+        <v>11.12458856178605</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.962374792069131</v>
+        <v>8.978082755337081</v>
       </c>
       <c r="C2" t="n">
-        <v>7.822565707438585</v>
+        <v>3.650137964389641</v>
       </c>
       <c r="D2" t="n">
-        <v>16.10458934046468</v>
+        <v>19.77043526812227</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.84727363096077</v>
+        <v>26.38937829015427</v>
       </c>
       <c r="C3" t="n">
-        <v>58.16855147662351</v>
+        <v>36.24612524079224</v>
       </c>
       <c r="D3" t="n">
-        <v>75.89891501532091</v>
+        <v>85.72620953483148</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.32047602440774</v>
+        <v>25.84450831429728</v>
       </c>
       <c r="C4" t="n">
-        <v>97.67309734781091</v>
+        <v>90.01546525468579</v>
       </c>
       <c r="D4" t="n">
-        <v>109.8997832565007</v>
+        <v>104.0799828657256</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.91371367968008</v>
+        <v>34.5820628820939</v>
       </c>
       <c r="C5" t="n">
-        <v>93.3396629812655</v>
+        <v>78.09802987283378</v>
       </c>
       <c r="D5" t="n">
-        <v>68.08420328951631</v>
+        <v>60.79472658548374</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.52333794628834</v>
+        <v>31.35603992593888</v>
       </c>
       <c r="C6" t="n">
-        <v>93.10208003683779</v>
+        <v>84.16621243278331</v>
       </c>
       <c r="D6" t="n">
-        <v>31.95981476405067</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="C7" t="n">
-        <v>75.27746871853267</v>
+        <v>71.56449890107125</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>53.07328089158257</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
         <v>29.04009709162065</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>18.41660518396592</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.457535487908019</v>
+        <v>5.205226327916588</v>
       </c>
       <c r="C2" t="n">
-        <v>3.453788423540279</v>
+        <v>1.789726064841935</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23944862884498</v>
+        <v>13.53241035533803</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.12001956629214</v>
+        <v>29.47206608148925</v>
       </c>
       <c r="C3" t="n">
-        <v>44.74806035956962</v>
+        <v>24.93148294934775</v>
       </c>
       <c r="D3" t="n">
-        <v>72.15354752361934</v>
+        <v>83.36019756759667</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>37.11399021134642</v>
       </c>
       <c r="C4" t="n">
-        <v>123.6452328636603</v>
+        <v>93.66560321907544</v>
       </c>
       <c r="D4" t="n">
-        <v>122.0881810047248</v>
+        <v>120.1610102612884</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.38066573400307</v>
+        <v>38.58268477689965</v>
       </c>
       <c r="C5" t="n">
-        <v>135.7757074973339</v>
+        <v>121.2458414744811</v>
       </c>
       <c r="D5" t="n">
-        <v>85.19115703601699</v>
+        <v>79.42338927356697</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.36611944488861</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="C6" t="n">
-        <v>120.0304378166235</v>
+        <v>105.2580801108218</v>
       </c>
       <c r="D6" t="n">
-        <v>40.13090090649688</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>98.45358677268713</v>
+        <v>92.34515255686348</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18023463808323</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>15.70599977254047</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.861033794353459</v>
+        <v>6.921321314940013</v>
       </c>
       <c r="C2" t="n">
-        <v>9.06742179642354</v>
+        <v>8.868127012461438</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7586132379423</v>
+        <v>24.25800402423444</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.26880324898115</v>
+        <v>23.67975462643307</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94053966286423</v>
+        <v>14.87347771933918</v>
       </c>
       <c r="D3" t="n">
-        <v>66.30233120630834</v>
+        <v>75.3638625165064</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.51109930994765</v>
+        <v>46.72431848821844</v>
       </c>
       <c r="C4" t="n">
-        <v>117.4170254279185</v>
+        <v>77.66115214444393</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8952186753447</v>
+        <v>133.1917475397563</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.65189014228245</v>
+        <v>47.02571503342222</v>
       </c>
       <c r="C5" t="n">
-        <v>183.1941216124548</v>
+        <v>147.5321362556895</v>
       </c>
       <c r="D5" t="n">
-        <v>107.0104997629024</v>
+        <v>101.7581495451819</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.93343074922303</v>
+        <v>45.48437113775474</v>
       </c>
       <c r="C6" t="n">
-        <v>165.1525440515112</v>
+        <v>149.21288832536</v>
       </c>
       <c r="D6" t="n">
-        <v>54.86300695642451</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.78171751895449</v>
       </c>
       <c r="C7" t="n">
-        <v>134.6849857979157</v>
+        <v>122.1686843164731</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>98.3858461810941</v>
+        <v>95.29824965123788</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>61.23749480009903</v>
+        <v>62.79061966821748</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.479313863850696</v>
+        <v>3.979023445312322</v>
       </c>
       <c r="C2" t="n">
-        <v>4.173409490753191</v>
+        <v>4.003567137918493</v>
       </c>
       <c r="D2" t="n">
-        <v>10.19839515171587</v>
+        <v>16.74763408674634</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.5780537758189</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="C3" t="n">
-        <v>33.0259927708627</v>
+        <v>24.60259746842507</v>
       </c>
       <c r="D3" t="n">
-        <v>66.18452148179873</v>
+        <v>78.69689597242433</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.62895009218627</v>
+        <v>52.26333903557895</v>
       </c>
       <c r="C4" t="n">
-        <v>112.3247000859903</v>
+        <v>70.38640165597508</v>
       </c>
       <c r="D4" t="n">
-        <v>134.519070435898</v>
+        <v>141.5513292414179</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.49266708774522</v>
+        <v>49.45554060143309</v>
       </c>
       <c r="C5" t="n">
-        <v>217.9234466501858</v>
+        <v>167.363439881475</v>
       </c>
       <c r="D5" t="n">
-        <v>112.3855684436536</v>
+        <v>110.5938788834032</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.52083467153211</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="C6" t="n">
-        <v>199.4469548562608</v>
+        <v>184.5538421828367</v>
       </c>
       <c r="D6" t="n">
-        <v>53.69570893607505</v>
+        <v>50.83784136901259</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7810171464826</v>
+        <v>128.6963248020101</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>77.10646469154449</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.90016483380309</v>
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.636794407157685</v>
+        <v>4.465970306618741</v>
       </c>
       <c r="C2" t="n">
-        <v>4.938190952361456</v>
+        <v>2.997275741065512</v>
       </c>
       <c r="D2" t="n">
-        <v>7.970809610779853</v>
+        <v>19.19611286113788</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="C3" t="n">
-        <v>24.51424017504286</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>59.67062546412114</v>
+        <v>74.76008767839461</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.46379549369455</v>
+        <v>51.22955870300706</v>
       </c>
       <c r="C4" t="n">
-        <v>97.53270742610363</v>
+        <v>65.77905967994479</v>
       </c>
       <c r="D4" t="n">
-        <v>137.8501403964074</v>
+        <v>147.5370449942107</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.98540662428588</v>
+        <v>62.29189183446013</v>
       </c>
       <c r="C5" t="n">
-        <v>214.6100481483528</v>
+        <v>150.4282919832175</v>
       </c>
       <c r="D5" t="n">
-        <v>130.0324834274901</v>
+        <v>132.045066221196</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.91834468076083</v>
+        <v>49.91205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>266.2647036072987</v>
+        <v>226.0935510449277</v>
       </c>
       <c r="D6" t="n">
-        <v>70.52090109145691</v>
+        <v>69.43410638285567</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>203.6743604707475</v>
+        <v>189.9004401801648</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9141906768949</v>
+        <v>117.5790137991192</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>53.91562042182632</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.264311116620644</v>
+        <v>3.125884690321844</v>
       </c>
       <c r="C2" t="n">
-        <v>2.819579406596839</v>
+        <v>1.769109363052752</v>
       </c>
       <c r="D2" t="n">
-        <v>6.324418710757953</v>
+        <v>13.45092529588555</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50947030524186</v>
+        <v>18.0052528958865</v>
       </c>
       <c r="C3" t="n">
-        <v>22.53601855098553</v>
+        <v>16.33137306014569</v>
       </c>
       <c r="D3" t="n">
-        <v>54.04521111878692</v>
+        <v>74.00414194612456</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.38423287192155</v>
+        <v>47.10720009287471</v>
       </c>
       <c r="C4" t="n">
-        <v>83.7489696584784</v>
+        <v>59.74229304653115</v>
       </c>
       <c r="D4" t="n">
-        <v>137.3013434297334</v>
+        <v>150.7532504733232</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.44039777970866</v>
+        <v>69.63045592370504</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4986686894164</v>
+        <v>143.8751260573701</v>
       </c>
       <c r="D5" t="n">
-        <v>144.1205629834318</v>
+        <v>146.7712817848982</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.6994970581718</v>
+        <v>59.2101857908294</v>
       </c>
       <c r="C6" t="n">
-        <v>303.8194985378519</v>
+        <v>242.2344650504495</v>
       </c>
       <c r="D6" t="n">
-        <v>83.36117931530093</v>
+        <v>84.72973561502099</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>264.698816019025</v>
+        <v>241.5825845748296</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>157.1336288032232</v>
+        <v>156.2156946997524</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>67.78280674431251</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.599487994396307</v>
+        <v>4.14886579814702</v>
       </c>
       <c r="C2" t="n">
-        <v>7.829437941368313</v>
+        <v>8.6030551323148</v>
       </c>
       <c r="D2" t="n">
-        <v>6.849653732529996</v>
+        <v>12.51335623832985</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.37769512869454</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="C3" t="n">
-        <v>17.07750131537327</v>
+        <v>11.79078992800419</v>
       </c>
       <c r="D3" t="n">
-        <v>47.89456175168064</v>
+        <v>68.2854615688869</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.85797504471626</v>
+        <v>41.23634882147878</v>
       </c>
       <c r="C4" t="n">
-        <v>71.36913110792612</v>
+        <v>50.85943981850601</v>
       </c>
       <c r="D4" t="n">
-        <v>133.5873918645677</v>
+        <v>152.5655567353628</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.43410638285567</v>
+        <v>70.09678608322227</v>
       </c>
       <c r="C5" t="n">
-        <v>185.0103548653114</v>
+        <v>128.6334929489384</v>
       </c>
       <c r="D5" t="n">
-        <v>155.8524480491812</v>
+        <v>162.9210315197582</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.45927197026759</v>
+        <v>73.09700706740053</v>
       </c>
       <c r="C6" t="n">
-        <v>315.8949953000877</v>
+        <v>237.5652729690517</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3536694910322</v>
+        <v>104.5738019609618</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.59071868498287</v>
+        <v>39.1059563032632</v>
       </c>
       <c r="C7" t="n">
-        <v>334.3469434014064</v>
+        <v>288.0545939030566</v>
       </c>
       <c r="D7" t="n">
-        <v>55.27534099220816</v>
+        <v>54.49681506274045</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>233.238710836436</v>
+        <v>224.8104067954771</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>110.7156155987298</v>
+        <v>116.3734276183041</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.75891633757857</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>24.87748682561417</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>12.29148125717007</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.98419422574081</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.006332454581986</v>
+        <v>5.099197575857933</v>
       </c>
       <c r="C2" t="n">
-        <v>5.016730768701201</v>
+        <v>4.202861921880595</v>
       </c>
       <c r="D2" t="n">
-        <v>9.592656818195584</v>
+        <v>5.575345212417637</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.291800052339555</v>
+        <v>2.907936699979052</v>
       </c>
       <c r="C2" t="n">
-        <v>4.510148953309847</v>
+        <v>4.748713645441821</v>
       </c>
       <c r="D2" t="n">
-        <v>5.041274461307371</v>
+        <v>9.210756961243575</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.23243752619501</v>
+        <v>19.27170743436489</v>
       </c>
       <c r="C3" t="n">
-        <v>23.52267499375358</v>
+        <v>20.5136182802371</v>
       </c>
       <c r="D3" t="n">
-        <v>51.62029428929728</v>
+        <v>72.93403694849555</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.41198384954772</v>
+        <v>54.81588306662066</v>
       </c>
       <c r="C4" t="n">
-        <v>103.250406055637</v>
+        <v>71.90516535444488</v>
       </c>
       <c r="D4" t="n">
-        <v>138.7052426468063</v>
+        <v>157.1856614315483</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.29507375728434</v>
+        <v>43.76140391680158</v>
       </c>
       <c r="C5" t="n">
-        <v>270.0051623604791</v>
+        <v>197.1594827053657</v>
       </c>
       <c r="D5" t="n">
-        <v>142.4761355788184</v>
+        <v>150.1092239793373</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.70193391300324</v>
+        <v>24.2717484920939</v>
       </c>
       <c r="C6" t="n">
-        <v>282.1238560217017</v>
+        <v>240.9464120624777</v>
       </c>
       <c r="D6" t="n">
-        <v>81.30834486572085</v>
+        <v>82.07312632732911</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>164.0294246778528</v>
+        <v>158.1006502919063</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>81.61268665403733</v>
+        <v>85.78511439708629</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
         <v>19.50241814486289</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>10.14636252339079</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.237043165079987</v>
+        <v>6.609125544989528</v>
       </c>
       <c r="C2" t="n">
-        <v>2.901064466049324</v>
+        <v>4.91561075516378</v>
       </c>
       <c r="D2" t="n">
-        <v>14.94612704945344</v>
+        <v>15.29072049364407</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7578114166873</v>
+        <v>10.83358591636355</v>
       </c>
       <c r="C3" t="n">
-        <v>12.64000169217768</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D3" t="n">
-        <v>11.19192382841364</v>
+        <v>8.040513697781376</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39846296892847</v>
+        <v>13.39945035417072</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14489436674317</v>
+        <v>70.15006361889378</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576289761050408</v>
+        <v>1.576405924020085</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.28474789196058</v>
+        <v>4.840997929641022</v>
       </c>
       <c r="C2" t="n">
-        <v>5.78347572571796</v>
+        <v>3.169081589308704</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0824100538945</v>
+        <v>13.96732458831937</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04943154257761</v>
+        <v>18.0052528958865</v>
       </c>
       <c r="C3" t="n">
-        <v>11.80551614356789</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="D3" t="n">
-        <v>21.03885330200914</v>
+        <v>18.93791321492097</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.83028082035232</v>
+        <v>12.66061839396687</v>
       </c>
       <c r="C4" t="n">
-        <v>20.11404696460865</v>
+        <v>17.1913840490659</v>
       </c>
       <c r="D4" t="n">
-        <v>20.930861054542</v>
+        <v>19.2844701545201</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44319055270643</v>
+        <v>15.44517111781599</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15674729404643</v>
+        <v>86.16779676255237</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251198011096092</v>
+        <v>3.251614972171788</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.46637121724624</v>
+        <v>4.775220833456485</v>
       </c>
       <c r="C2" t="n">
-        <v>5.884595739255381</v>
+        <v>3.624612524079224</v>
       </c>
       <c r="D2" t="n">
-        <v>33.11533181194916</v>
+        <v>19.35417424152162</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.19669369821463</v>
+        <v>17.34748193404114</v>
       </c>
       <c r="C3" t="n">
-        <v>18.29486846863931</v>
+        <v>13.94572613882594</v>
       </c>
       <c r="D3" t="n">
-        <v>29.82058651649687</v>
+        <v>25.7168811127452</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.15081359802229</v>
+        <v>25.55096575072749</v>
       </c>
       <c r="C4" t="n">
-        <v>25.67859295227957</v>
+        <v>30.6560538128109</v>
       </c>
       <c r="D4" t="n">
-        <v>26.77618688562751</v>
+        <v>24.26193101505142</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.17996292951343</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="C5" t="n">
-        <v>23.4392264388926</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
         <v>12.19625172985813</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5277,7 +5277,7 @@
         <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74075453713811</v>
+        <v>16.7451121635145</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1186026765425</v>
+        <v>102.1451841974385</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022226361141434</v>
+        <v>5.02353364905435</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.367615609744812</v>
+        <v>5.777585239492479</v>
       </c>
       <c r="C2" t="n">
-        <v>4.925428232206248</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="D2" t="n">
-        <v>27.93268568123025</v>
+        <v>22.26603793231766</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49121800948867</v>
+        <v>16.99896149903352</v>
       </c>
       <c r="C3" t="n">
-        <v>20.90631736193583</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="D3" t="n">
-        <v>48.35598317267664</v>
+        <v>34.70478134512475</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.97512181669111</v>
+        <v>29.81371428256714</v>
       </c>
       <c r="C4" t="n">
-        <v>36.65453228575891</v>
+        <v>33.08097064230052</v>
       </c>
       <c r="D4" t="n">
-        <v>34.95709050511617</v>
+        <v>31.05169813762236</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.50718801466389</v>
+        <v>25.08365384350601</v>
       </c>
       <c r="C5" t="n">
-        <v>36.64373306101221</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="D5" t="n">
-        <v>32.96217917008666</v>
+        <v>31.90680038802134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.87423848286517</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>25.39879485656924</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>44.07556318216055</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0707988815401</v>
+        <v>18.08147621857061</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8904498462378</v>
+        <v>117.9601067592464</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884113859634322</v>
+        <v>6.888181416598328</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.093528073810704</v>
+        <v>7.430848373444108</v>
       </c>
       <c r="C2" t="n">
-        <v>11.59836737797182</v>
+        <v>6.870270434319178</v>
       </c>
       <c r="D2" t="n">
-        <v>22.59590516094459</v>
+        <v>27.67644953042183</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24578108342697</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6973850273805</v>
+        <v>20.84741249968102</v>
       </c>
       <c r="D3" t="n">
-        <v>55.34602682691393</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.69586350032851</v>
+        <v>22.96013355922015</v>
       </c>
       <c r="C4" t="n">
-        <v>38.19882142453914</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D4" t="n">
-        <v>43.76336741221007</v>
+        <v>35.42931115085889</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.40839134943345</v>
+        <v>21.77025534167302</v>
       </c>
       <c r="C5" t="n">
-        <v>39.88350048502668</v>
+        <v>38.63177216211199</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>28.73968229412113</v>
+        <v>30.47050349670826</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>18.80439552714341</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065094087422507</v>
+        <v>7.071979937650489</v>
       </c>
       <c r="C21" t="n">
-        <v>66.235257069586</v>
+        <v>67.18380940767965</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29882056556688</v>
+        <v>5.303984953237867</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.39903153628071</v>
+        <v>5.191481860057134</v>
       </c>
       <c r="C2" t="n">
-        <v>7.107853378746906</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="D2" t="n">
-        <v>21.23618459056275</v>
+        <v>25.84745355741002</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.78422079371073</v>
+        <v>22.57037972063417</v>
       </c>
       <c r="C3" t="n">
-        <v>36.15285920888879</v>
+        <v>24.86276061005047</v>
       </c>
       <c r="D3" t="n">
-        <v>61.32487034577701</v>
+        <v>55.28221322613789</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.51115606320987</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="C4" t="n">
-        <v>43.80165557267569</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D4" t="n">
-        <v>63.57110909309371</v>
+        <v>49.54487964251953</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39138284329177</v>
+        <v>29.40334374219198</v>
       </c>
       <c r="C5" t="n">
-        <v>59.02758071783948</v>
+        <v>47.51658888554563</v>
       </c>
       <c r="D5" t="n">
-        <v>40.74252972624264</v>
+        <v>35.85833489761475</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.18495378349268</v>
+        <v>22.62143060125501</v>
       </c>
       <c r="C6" t="n">
-        <v>49.46928506929254</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="D6" t="n">
-        <v>33.93214590188251</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>32.21899615797182</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="D7" t="n">
         <v>33.71616140694821</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>22.78145547704723</v>
+        <v>21.94696992843745</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290952109886349</v>
+        <v>7.30134575556263</v>
       </c>
       <c r="C21" t="n">
-        <v>76.55499715380667</v>
+        <v>77.57679865285294</v>
       </c>
       <c r="D21" t="n">
-        <v>6.379583096150555</v>
+        <v>6.388677536117301</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.449681506274044</v>
+        <v>4.787001805907448</v>
       </c>
       <c r="C2" t="n">
-        <v>5.107051557491907</v>
+        <v>7.702792487520473</v>
       </c>
       <c r="D2" t="n">
-        <v>27.31909336607599</v>
+        <v>27.87279907127119</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35577788403162</v>
+        <v>20.01292695107123</v>
       </c>
       <c r="C3" t="n">
-        <v>30.93977889933823</v>
+        <v>24.97075285751762</v>
       </c>
       <c r="D3" t="n">
-        <v>64.08358139471055</v>
+        <v>63.63688618927824</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.40226418349649</v>
+        <v>38.22434686484957</v>
       </c>
       <c r="C4" t="n">
-        <v>71.80306359320322</v>
+        <v>55.13495107050087</v>
       </c>
       <c r="D4" t="n">
-        <v>79.43517024601793</v>
+        <v>67.01704353500003</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.15348110369455</v>
+        <v>37.62548076525901</v>
       </c>
       <c r="C5" t="n">
-        <v>71.8148445656542</v>
+        <v>67.44606728175589</v>
       </c>
       <c r="D5" t="n">
-        <v>55.14967728606459</v>
+        <v>46.16668579220627</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>32.6440929139107</v>
       </c>
       <c r="C6" t="n">
-        <v>74.3045567436241</v>
+        <v>63.87937787222722</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>53.77817574323178</v>
+        <v>55.39511421212627</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>34.21390749300134</v>
+        <v>35.13184159647211</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.504557576083378</v>
+        <v>7.51974026524965</v>
       </c>
       <c r="C21" t="n">
-        <v>86.30241212495883</v>
+        <v>87.41698058352718</v>
       </c>
       <c r="D21" t="n">
-        <v>7.504557576083378</v>
+        <v>7.51974026524965</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613320512</v>
+        <v>10.84497636289614</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907124846393</v>
+        <v>37.78907204881703</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.013204688511713</v>
+        <v>4.21366114662731</v>
       </c>
       <c r="C2" t="n">
-        <v>6.110397711232148</v>
+        <v>6.984153168011809</v>
       </c>
       <c r="D2" t="n">
-        <v>31.33935021496668</v>
+        <v>25.85727103445249</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.03470532701391</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C3" t="n">
-        <v>27.86690858504571</v>
+        <v>24.6075062069463</v>
       </c>
       <c r="D3" t="n">
-        <v>70.66619975168541</v>
+        <v>73.87160600605124</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.41578766717769</v>
+        <v>30.79644373451819</v>
       </c>
       <c r="C4" t="n">
-        <v>59.33388600156448</v>
+        <v>57.89169862402591</v>
       </c>
       <c r="D4" t="n">
-        <v>82.28125684062942</v>
+        <v>102.3187274843068</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.27744335633691</v>
+        <v>40.44800541496859</v>
       </c>
       <c r="C5" t="n">
-        <v>86.39379797371933</v>
+        <v>130.1061145053086</v>
       </c>
       <c r="D5" t="n">
-        <v>59.8375225738431</v>
+        <v>76.52723354603889</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>86.29955019411163</v>
+        <v>180.2469150043059</v>
       </c>
       <c r="D6" t="n">
-        <v>43.39128503230054</v>
+        <v>48.62400029593603</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.12296480940488</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>75.51701515836889</v>
+        <v>166.2452292463379</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>55.66018609227291</v>
+        <v>104.5610392408065</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.724771888788264</v>
+        <v>7.63279821140476</v>
       </c>
       <c r="C21" t="n">
-        <v>96.5596486098533</v>
+        <v>91.59357853685712</v>
       </c>
       <c r="D21" t="n">
-        <v>8.690368374886797</v>
+        <v>7.63279821140476</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.747952881915827</v>
+        <v>5.131595250098078</v>
       </c>
       <c r="C2" t="n">
-        <v>5.932701376763475</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89966611218435</v>
+        <v>29.01555339901448</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.34042977366217</v>
+        <v>14.63785827031994</v>
       </c>
       <c r="C3" t="n">
-        <v>25.54998400302324</v>
+        <v>25.64815877344792</v>
       </c>
       <c r="D3" t="n">
-        <v>78.19129590473722</v>
+        <v>76.1148995102552</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.15678619970578</v>
+        <v>29.67332436085984</v>
       </c>
       <c r="C4" t="n">
-        <v>64.06885517914685</v>
+        <v>58.87442807597697</v>
       </c>
       <c r="D4" t="n">
-        <v>97.30297846330987</v>
+        <v>112.0056320821101</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.7443954106599</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="C5" t="n">
-        <v>98.1502267320749</v>
+        <v>119.0859965251381</v>
       </c>
       <c r="D5" t="n">
-        <v>73.48381566287377</v>
+        <v>92.65243958829274</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>111.4568351154361</v>
+        <v>190.7928488433252</v>
       </c>
       <c r="D6" t="n">
-        <v>51.72337779824321</v>
+        <v>58.56615929684348</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.88448223273092</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>99.05245287227768</v>
+        <v>209.1240419770216</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.78283813537898</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C8" t="n">
-        <v>77.94095024015427</v>
+        <v>154.5467236025329</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>51.9187455913883</v>
+        <v>85.75468021825461</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>36.58482819875739</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.915040634321652</v>
+        <v>7.800678011959</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8636684840521</v>
+        <v>99.45864465247725</v>
       </c>
       <c r="D21" t="n">
-        <v>9.893800792902065</v>
+        <v>8.775762763453876</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.11789183996763</v>
+        <v>6.904631603967817</v>
       </c>
       <c r="C2" t="n">
-        <v>5.497787143782138</v>
+        <v>11.55517047898496</v>
       </c>
       <c r="D2" t="n">
-        <v>24.20302615279661</v>
+        <v>23.74062298409637</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.28076414788136</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14117604742907</v>
+        <v>24.852943133008</v>
       </c>
       <c r="D3" t="n">
-        <v>78.3483755374167</v>
+        <v>79.51665530547041</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.92705723691203</v>
+        <v>28.10350978176919</v>
       </c>
       <c r="C4" t="n">
-        <v>63.20099020859267</v>
+        <v>60.30385273336033</v>
       </c>
       <c r="D4" t="n">
-        <v>109.6828170138621</v>
+        <v>120.9650616310665</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.79977419272522</v>
+        <v>43.44233591292137</v>
       </c>
       <c r="C5" t="n">
-        <v>107.4031988446011</v>
+        <v>114.2263453891164</v>
       </c>
       <c r="D5" t="n">
-        <v>88.70090507869934</v>
+        <v>105.4397034361075</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.38377520803183</v>
+        <v>48.82525857530663</v>
       </c>
       <c r="C6" t="n">
-        <v>130.6971266232651</v>
+        <v>189.0217759848639</v>
       </c>
       <c r="D6" t="n">
-        <v>60.41773546705297</v>
+        <v>70.3196428120863</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.54429880544279</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="C7" t="n">
-        <v>127.7980256526243</v>
+        <v>235.534036968965</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.46148784092078</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C8" t="n">
-        <v>101.8072369303942</v>
+        <v>205.366893512869</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>127.0234267139735</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>66.76375262730434</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>39.626282586514</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.090609863117125</v>
+        <v>7.95323281751981</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2798643165294</v>
+        <v>106.3744889343275</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12458856178605</v>
+        <v>9.941541021899763</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.978082755337081</v>
+        <v>6.23606141737574</v>
       </c>
       <c r="C2" t="n">
-        <v>3.650137964389641</v>
+        <v>8.041495445485625</v>
       </c>
       <c r="D2" t="n">
-        <v>19.77043526812227</v>
+        <v>19.75570905255857</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.38937829015427</v>
+        <v>18.76610736667778</v>
       </c>
       <c r="C3" t="n">
-        <v>36.24612524079224</v>
+        <v>39.88350048502667</v>
       </c>
       <c r="D3" t="n">
-        <v>85.72620953483148</v>
+        <v>86.81104074802421</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.84450831429728</v>
+        <v>20.86704745376596</v>
       </c>
       <c r="C4" t="n">
-        <v>90.01546525468579</v>
+        <v>88.85405772056183</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0799828657256</v>
+        <v>116.8554657410893</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.5820628820939</v>
+        <v>27.4889357189107</v>
       </c>
       <c r="C5" t="n">
-        <v>78.09802987283378</v>
+        <v>112.9500733735956</v>
       </c>
       <c r="D5" t="n">
-        <v>60.79472658548374</v>
+        <v>70.34222300928397</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.35603992593888</v>
+        <v>24.43275511559037</v>
       </c>
       <c r="C6" t="n">
-        <v>84.16621243278331</v>
+        <v>155.1298817388555</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>71.56449890107125</v>
+        <v>144.3866166112826</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>53.49052366588747</v>
+        <v>93.6292785540183</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>50.9203081761693</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.72062817711293</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.205226327916588</v>
+        <v>3.669772918474577</v>
       </c>
       <c r="C2" t="n">
-        <v>1.789726064841935</v>
+        <v>3.963315482044373</v>
       </c>
       <c r="D2" t="n">
-        <v>13.53241035533803</v>
+        <v>14.48372388075319</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.47206608148925</v>
+        <v>20.43998720241859</v>
       </c>
       <c r="C3" t="n">
-        <v>24.93148294934775</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="D3" t="n">
-        <v>83.36019756759667</v>
+        <v>83.47800729210628</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.11399021134642</v>
+        <v>27.22288209105981</v>
       </c>
       <c r="C4" t="n">
-        <v>93.66560321907544</v>
+        <v>97.11153766098174</v>
       </c>
       <c r="D4" t="n">
-        <v>120.1610102612884</v>
+        <v>131.2135259156989</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.58268477689965</v>
+        <v>30.55689729468198</v>
       </c>
       <c r="C5" t="n">
-        <v>121.2458414744811</v>
+        <v>138.819125380499</v>
       </c>
       <c r="D5" t="n">
-        <v>79.42338927356697</v>
+        <v>87.3264582927538</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>105.2580801108218</v>
+        <v>172.9613652910903</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>39.52712606838509</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>14.61233283000952</v>
       </c>
       <c r="C7" t="n">
-        <v>92.34515255686348</v>
+        <v>179.0609637775758</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>122.8362727553609</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>54.91405783704532</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.921321314940013</v>
+        <v>4.472842540548468</v>
       </c>
       <c r="C2" t="n">
-        <v>8.868127012461438</v>
+        <v>5.931719629059228</v>
       </c>
       <c r="D2" t="n">
-        <v>24.25800402423444</v>
+        <v>17.9905266803228</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.67975462643307</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="C3" t="n">
-        <v>14.87347771933918</v>
+        <v>25.38308689330128</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3638625165064</v>
+        <v>76.36033643631691</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.72431848821844</v>
+        <v>32.72361447795468</v>
       </c>
       <c r="C4" t="n">
-        <v>77.66115214444393</v>
+        <v>94.80148531288899</v>
       </c>
       <c r="D4" t="n">
-        <v>133.1917475397563</v>
+        <v>141.2194985173824</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02571503342222</v>
+        <v>34.85204350076177</v>
       </c>
       <c r="C5" t="n">
-        <v>147.5321362556895</v>
+        <v>157.5459628390069</v>
       </c>
       <c r="D5" t="n">
-        <v>101.7581495451819</v>
+        <v>110.0048302608551</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.48437113775474</v>
+        <v>34.57617239586842</v>
       </c>
       <c r="C6" t="n">
-        <v>149.21288832536</v>
+        <v>194.9387693983594</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>53.89696721544566</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78171751895449</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="C7" t="n">
-        <v>122.1686843164731</v>
+        <v>213.6754243339098</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>95.29824965123788</v>
+        <v>173.572994110836</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>62.79061966821748</v>
+        <v>94.62967946464578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.74146586308036</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>33.70830742531424</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.979023445312322</v>
+        <v>2.644828315240907</v>
       </c>
       <c r="C2" t="n">
-        <v>4.003567137918493</v>
+        <v>2.845104846907257</v>
       </c>
       <c r="D2" t="n">
-        <v>16.74763408674634</v>
+        <v>12.55557138961246</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.52544031041707</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="C3" t="n">
-        <v>24.60259746842507</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D3" t="n">
-        <v>78.69689597242433</v>
+        <v>76.06090338652164</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.26333903557895</v>
+        <v>35.76114187489431</v>
       </c>
       <c r="C4" t="n">
-        <v>70.38640165597508</v>
+        <v>93.70389137954106</v>
       </c>
       <c r="D4" t="n">
-        <v>141.5513292414179</v>
+        <v>149.1961986143878</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.45554060143309</v>
+        <v>36.52101459798135</v>
       </c>
       <c r="C5" t="n">
-        <v>167.363439881475</v>
+        <v>188.3482970597506</v>
       </c>
       <c r="D5" t="n">
-        <v>110.5938788834032</v>
+        <v>115.895316486336</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.44033135978387</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5538421828367</v>
+        <v>235.4319352077234</v>
       </c>
       <c r="D6" t="n">
-        <v>50.83784136901259</v>
+        <v>52.56866257159972</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>128.6963248020101</v>
+        <v>223.616601587113</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>77.10646469154449</v>
+        <v>120.7500588838364</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
+        <v>34.94530953266521</v>
+      </c>
+      <c r="D9" t="n">
         <v>31.28437234352885</v>
-      </c>
-      <c r="D9" t="n">
-        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.465970306618741</v>
+        <v>2.703733177495716</v>
       </c>
       <c r="C2" t="n">
-        <v>2.997275741065512</v>
+        <v>4.039891802975625</v>
       </c>
       <c r="D2" t="n">
-        <v>19.19611286113788</v>
+        <v>11.70635962543897</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67422399310608</v>
+        <v>13.39594742444773</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>18.57957530287089</v>
       </c>
       <c r="D3" t="n">
-        <v>74.76008767839461</v>
+        <v>69.87098411124549</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.22955870300706</v>
+        <v>34.40829353844221</v>
       </c>
       <c r="C4" t="n">
-        <v>65.77905967994479</v>
+        <v>79.77976369020855</v>
       </c>
       <c r="D4" t="n">
-        <v>147.5370449942107</v>
+        <v>152.1188615299305</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.29189183446013</v>
+        <v>43.78594760940775</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4282919832175</v>
+        <v>182.6296166825129</v>
       </c>
       <c r="D5" t="n">
-        <v>132.045066221196</v>
+        <v>136.9783484350363</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>35.86422538384024</v>
       </c>
       <c r="C6" t="n">
-        <v>226.0935510449277</v>
+        <v>268.2370347451306</v>
       </c>
       <c r="D6" t="n">
-        <v>69.43410638285567</v>
+        <v>70.84291433844986</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9004401801648</v>
+        <v>274.1010137825967</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>117.5790137991192</v>
+        <v>190.3461536378928</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>56.57812019574367</v>
+        <v>75.32655610374501</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.125884690321844</v>
+        <v>1.830959468420301</v>
       </c>
       <c r="C2" t="n">
-        <v>1.769109363052752</v>
+        <v>4.006512381031233</v>
       </c>
       <c r="D2" t="n">
-        <v>13.45092529588555</v>
+        <v>9.744827712353841</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.0052528958865</v>
+        <v>11.77606371244049</v>
       </c>
       <c r="C3" t="n">
-        <v>16.33137306014569</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="D3" t="n">
-        <v>74.00414194612456</v>
+        <v>65.37948836431633</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.10720009287471</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>59.74229304653115</v>
+        <v>67.25953521794898</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7532504733232</v>
+        <v>152.6293703361389</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.63045592370504</v>
+        <v>47.98291904506286</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8751260573701</v>
+        <v>175.4628584415112</v>
       </c>
       <c r="D5" t="n">
-        <v>146.7712817848982</v>
+        <v>150.5510104462484</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.2101857908294</v>
+        <v>41.90197376495812</v>
       </c>
       <c r="C6" t="n">
-        <v>242.2344650504495</v>
+        <v>288.8861342085538</v>
       </c>
       <c r="D6" t="n">
-        <v>84.72973561502099</v>
+        <v>85.33351045313277</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>241.5825845748296</v>
+        <v>322.1899615797182</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>156.2156946997524</v>
+        <v>237.9952784635118</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>67.78280674431251</v>
+        <v>85.53280523709483</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.14886579814702</v>
+        <v>2.54861704022472</v>
       </c>
       <c r="C2" t="n">
-        <v>8.6030551323148</v>
+        <v>6.663121668723102</v>
       </c>
       <c r="D2" t="n">
-        <v>12.51335623832985</v>
+        <v>14.34038871593316</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.38260386721577</v>
+        <v>9.154797342101507</v>
       </c>
       <c r="C3" t="n">
-        <v>11.79078992800419</v>
+        <v>16.69952844923824</v>
       </c>
       <c r="D3" t="n">
-        <v>68.2854615688869</v>
+        <v>59.19447782756144</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.23634882147878</v>
+        <v>27.08249216935251</v>
       </c>
       <c r="C4" t="n">
-        <v>50.85943981850601</v>
+        <v>57.01107093331653</v>
       </c>
       <c r="D4" t="n">
-        <v>152.5655567353628</v>
+        <v>150.4852333500639</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.09678608322227</v>
+        <v>48.03200643027521</v>
       </c>
       <c r="C5" t="n">
-        <v>128.6334929489384</v>
+        <v>153.6435157146258</v>
       </c>
       <c r="D5" t="n">
-        <v>162.9210315197582</v>
+        <v>165.1790512395259</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.09700706740053</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="C6" t="n">
-        <v>237.5652729690517</v>
+        <v>286.0685182973654</v>
       </c>
       <c r="D6" t="n">
-        <v>104.5738019609618</v>
+        <v>104.3725436815912</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.1059563032632</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="C7" t="n">
-        <v>288.0545939030566</v>
+        <v>361.0563714431452</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>52.70021676396878</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>224.8104067954771</v>
+        <v>312.5148379543659</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>116.3734276183041</v>
+        <v>157.8640490951828</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>54.8060655895782</v>
       </c>
       <c r="D10" t="n">
-        <v>27.75891633757857</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.099197575857933</v>
+        <v>4.458116324984766</v>
       </c>
       <c r="C2" t="n">
-        <v>4.202861921880595</v>
+        <v>11.98517597344506</v>
       </c>
       <c r="D2" t="n">
-        <v>5.575345212417637</v>
+        <v>11.2792993740916</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.907936699979052</v>
+        <v>1.842740440871263</v>
       </c>
       <c r="C2" t="n">
-        <v>4.748713645441821</v>
+        <v>3.837651775900782</v>
       </c>
       <c r="D2" t="n">
-        <v>9.210756961243575</v>
+        <v>10.66865230205009</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.27170743436489</v>
+        <v>12.18839774822415</v>
       </c>
       <c r="C3" t="n">
-        <v>20.5136182802371</v>
+        <v>21.88806506618264</v>
       </c>
       <c r="D3" t="n">
-        <v>72.93403694849555</v>
+        <v>64.72662614099221</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.81588306662066</v>
+        <v>36.92254940901829</v>
       </c>
       <c r="C4" t="n">
-        <v>71.90516535444488</v>
+        <v>84.20842758406592</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1856614315483</v>
+        <v>154.964948124542</v>
       </c>
     </row>
     <row r="5">
@@ -4243,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.76140391680158</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="C5" t="n">
-        <v>197.1594827053657</v>
+        <v>237.263876423848</v>
       </c>
       <c r="D5" t="n">
         <v>150.1092239793373</v>
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.2717484920939</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="C6" t="n">
-        <v>240.9464120624777</v>
+        <v>291.0597236257562</v>
       </c>
       <c r="D6" t="n">
-        <v>82.07312632732911</v>
+        <v>81.30834486572085</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>158.1006502919063</v>
+        <v>219.7838585497334</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>85.78511439708629</v>
+        <v>116.3272854762046</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.34596040698915</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.609125544989528</v>
+        <v>5.297510612115789</v>
       </c>
       <c r="C2" t="n">
-        <v>4.91561075516378</v>
+        <v>11.26751840164064</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29072049364407</v>
+        <v>18.70327551360598</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.83358591636355</v>
+        <v>9.47386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>10.75504610002381</v>
+        <v>30.19855938263188</v>
       </c>
       <c r="D3" t="n">
-        <v>8.040513697781376</v>
+        <v>12.61054926105028</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39945035417072</v>
+        <v>13.39724346825993</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15006361889378</v>
+        <v>70.13850992206669</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576405924020085</v>
+        <v>1.576146290383521</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.840997929641022</v>
+        <v>4.900884539600077</v>
       </c>
       <c r="C2" t="n">
-        <v>3.169081589308704</v>
+        <v>7.196210672129119</v>
       </c>
       <c r="D2" t="n">
-        <v>13.96732458831937</v>
+        <v>31.47581314585699</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.0052528958865</v>
+        <v>14.7605767333508</v>
       </c>
       <c r="C3" t="n">
-        <v>16.11047982669016</v>
+        <v>38.79866927183394</v>
       </c>
       <c r="D3" t="n">
-        <v>18.93791321492097</v>
+        <v>25.2701859073129</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.66061839396687</v>
+        <v>11.12909197534184</v>
       </c>
       <c r="C4" t="n">
-        <v>17.1913840490659</v>
+        <v>46.55840312620073</v>
       </c>
       <c r="D4" t="n">
-        <v>19.2844701545201</v>
+        <v>21.6838615436993</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44517111781599</v>
+        <v>15.436750114463</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16779676255237</v>
+        <v>86.12081642805673</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251614972171788</v>
+        <v>3.249842129360631</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.775220833456485</v>
+        <v>5.602834148136546</v>
       </c>
       <c r="C2" t="n">
-        <v>3.624612524079224</v>
+        <v>11.90172741858408</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35417424152162</v>
+        <v>30.11609257547515</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.34748193404114</v>
+        <v>15.94849145548944</v>
       </c>
       <c r="C3" t="n">
-        <v>13.94572613882594</v>
+        <v>32.33876937788994</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7168811127452</v>
+        <v>44.5860719883689</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.55096575072749</v>
+        <v>20.71389481190345</v>
       </c>
       <c r="C4" t="n">
-        <v>30.6560538128109</v>
+        <v>75.8233204420939</v>
       </c>
       <c r="D4" t="n">
-        <v>24.26193101505142</v>
+        <v>29.46912083837651</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.48644813968768</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="C5" t="n">
-        <v>20.66578917439536</v>
+        <v>50.56000676871075</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7451121635145</v>
+        <v>16.72107527038823</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1451841974385</v>
+        <v>101.1625053858488</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02353364905435</v>
+        <v>4.180268817597057</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.777585239492479</v>
+        <v>5.636213570080939</v>
       </c>
       <c r="C2" t="n">
-        <v>7.200137662946108</v>
+        <v>7.714573459971436</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26603793231766</v>
+        <v>30.53529884518854</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99896149903352</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01935721664445</v>
+        <v>40.46273163053229</v>
       </c>
       <c r="D3" t="n">
-        <v>34.70478134512475</v>
+        <v>56.77937847511428</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.81371428256714</v>
+        <v>25.78069471352124</v>
       </c>
       <c r="C4" t="n">
-        <v>33.08097064230052</v>
+        <v>77.78877934599602</v>
       </c>
       <c r="D4" t="n">
-        <v>31.05169813762236</v>
+        <v>43.22733316569131</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.08365384350601</v>
+        <v>20.24854640009047</v>
       </c>
       <c r="C5" t="n">
-        <v>40.25165587411923</v>
+        <v>97.95387719122553</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>34.26299487821369</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>23.30570875111504</v>
+        <v>46.61141750223008</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
         <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.46575898910303</v>
@@ -5591,7 +5591,7 @@
         <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08147621857061</v>
+        <v>18.03034071150518</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9601067592464</v>
+        <v>116.7679207983193</v>
       </c>
       <c r="D21" t="n">
-        <v>6.888181416598328</v>
+        <v>6.010113570501727</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.430848373444108</v>
+        <v>5.348561492736622</v>
       </c>
       <c r="C2" t="n">
-        <v>6.870270434319178</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="D2" t="n">
-        <v>27.67644953042183</v>
+        <v>25.80327491071892</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84741249968102</v>
+        <v>32.43694414831462</v>
       </c>
       <c r="D3" t="n">
-        <v>41.30703465618455</v>
+        <v>62.66495596207391</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.96013355922015</v>
+        <v>21.64557338323367</v>
       </c>
       <c r="C4" t="n">
-        <v>28.42257778564941</v>
+        <v>75.46596427774806</v>
       </c>
       <c r="D4" t="n">
-        <v>35.42931115085889</v>
+        <v>51.8932201510779</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.77025534167302</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C5" t="n">
-        <v>38.63177216211199</v>
+        <v>89.43721585688444</v>
       </c>
       <c r="D5" t="n">
-        <v>29.18245050873644</v>
+        <v>33.72303364087794</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.02266231265569</v>
       </c>
       <c r="C6" t="n">
-        <v>30.47050349670826</v>
+        <v>68.50831829775093</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>17.72643654788041</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.52187317249857</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.071979937650489</v>
+        <v>7.038716853856241</v>
       </c>
       <c r="C21" t="n">
-        <v>67.18380940767965</v>
+        <v>65.98797050490226</v>
       </c>
       <c r="D21" t="n">
-        <v>5.303984953237867</v>
+        <v>4.39919803366015</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.191481860057134</v>
+        <v>4.262748531839651</v>
       </c>
       <c r="C2" t="n">
-        <v>6.42062998577414</v>
+        <v>3.975096454495335</v>
       </c>
       <c r="D2" t="n">
-        <v>25.84745355741002</v>
+        <v>24.01354884587698</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57037972063417</v>
+        <v>17.71563732313369</v>
       </c>
       <c r="C3" t="n">
-        <v>24.86276061005047</v>
+        <v>24.55841882173396</v>
       </c>
       <c r="D3" t="n">
-        <v>55.28221322613789</v>
+        <v>69.19848693383643</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.29044275620359</v>
+        <v>27.8099672181994</v>
       </c>
       <c r="C4" t="n">
-        <v>43.91652005407257</v>
+        <v>79.0905768018273</v>
       </c>
       <c r="D4" t="n">
-        <v>49.54487964251953</v>
+        <v>72.69645400406782</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.89359569950963</v>
       </c>
       <c r="C5" t="n">
-        <v>47.51658888554563</v>
+        <v>119.1105402177443</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85833489761475</v>
+        <v>45.38128762880881</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.62143060125501</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>49.30827844579606</v>
+        <v>109.7662655687232</v>
       </c>
       <c r="D6" t="n">
-        <v>33.44912603139308</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.95924962250714</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>33.65627479698915</v>
+        <v>68.45039518320036</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>21.94696992843745</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>35.00617789032851</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.30134575556263</v>
+        <v>7.251261286679978</v>
       </c>
       <c r="C21" t="n">
-        <v>77.57679865285294</v>
+        <v>75.23183584930477</v>
       </c>
       <c r="D21" t="n">
-        <v>6.388677536117301</v>
+        <v>5.438445965009984</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.787001805907448</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C2" t="n">
-        <v>7.702792487520473</v>
+        <v>7.560439070404686</v>
       </c>
       <c r="D2" t="n">
-        <v>27.87279907127119</v>
+        <v>22.85999529338698</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.01292695107123</v>
+        <v>16.01230505626548</v>
       </c>
       <c r="C3" t="n">
-        <v>24.97075285751762</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63688618927824</v>
+        <v>72.05537275319465</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.22434686484957</v>
+        <v>31.47286790274425</v>
       </c>
       <c r="C4" t="n">
-        <v>55.13495107050087</v>
+        <v>68.484756352849</v>
       </c>
       <c r="D4" t="n">
-        <v>67.01704353500003</v>
+        <v>90.04099069499621</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.62548076525901</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>67.44606728175589</v>
+        <v>134.0331053222958</v>
       </c>
       <c r="D5" t="n">
-        <v>46.16668579220627</v>
+        <v>59.86206626644928</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>26.84785446803753</v>
       </c>
       <c r="C6" t="n">
-        <v>63.87937787222722</v>
+        <v>152.0707558924225</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>55.39511421212627</v>
+        <v>115.1619509512636</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>35.13184159647211</v>
+        <v>61.58503348740241</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.51974026524965</v>
+        <v>7.449546870891117</v>
       </c>
       <c r="C21" t="n">
-        <v>87.41698058352718</v>
+        <v>83.80740229752507</v>
       </c>
       <c r="D21" t="n">
-        <v>7.51974026524965</v>
+        <v>6.518353512029727</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_20_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636289614</v>
+        <v>10.84497629340496</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907204881703</v>
+        <v>37.7890718066766</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.21366114662731</v>
+        <v>0.6587527095496097</v>
       </c>
       <c r="C2" t="n">
-        <v>6.984153168011809</v>
+        <v>3.937790041733956</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85727103445249</v>
+        <v>13.45976102522377</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.52143120414207</v>
+        <v>6.430447462816608</v>
       </c>
       <c r="C3" t="n">
-        <v>24.6075062069463</v>
+        <v>46.33849164044945</v>
       </c>
       <c r="D3" t="n">
-        <v>73.87160600605124</v>
+        <v>69.80226177194821</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.79644373451819</v>
+        <v>13.34980528234813</v>
       </c>
       <c r="C4" t="n">
-        <v>57.89169862402591</v>
+        <v>133.5235782637917</v>
       </c>
       <c r="D4" t="n">
-        <v>102.3187274843068</v>
+        <v>81.06879842588461</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.44800541496859</v>
+        <v>13.40085616296897</v>
       </c>
       <c r="C5" t="n">
-        <v>130.1061145053086</v>
+        <v>160.147594255261</v>
       </c>
       <c r="D5" t="n">
-        <v>76.52723354603889</v>
+        <v>47.39387042251478</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>9.056622571676828</v>
       </c>
       <c r="C6" t="n">
-        <v>180.2469150043059</v>
+        <v>110.0077755039679</v>
       </c>
       <c r="D6" t="n">
-        <v>48.62400029593603</v>
+        <v>29.42396044398116</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>166.2452292463379</v>
+        <v>53.83806235319084</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>104.5610392408065</v>
+        <v>30.0414797499524</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.63279821140476</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91.59357853685712</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.63279821140476</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.131595250098078</v>
+        <v>0.7579092276785376</v>
       </c>
       <c r="C2" t="n">
-        <v>6.292021036517808</v>
+        <v>11.73581205656637</v>
       </c>
       <c r="D2" t="n">
-        <v>29.01555339901448</v>
+        <v>22.80894441276615</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.63785827031994</v>
+        <v>4.275511251994859</v>
       </c>
       <c r="C3" t="n">
-        <v>25.64815877344792</v>
+        <v>28.67685044104933</v>
       </c>
       <c r="D3" t="n">
-        <v>76.1148995102552</v>
+        <v>65.17332134642452</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.67332436085984</v>
+        <v>12.96692367769187</v>
       </c>
       <c r="C4" t="n">
-        <v>58.87442807597697</v>
+        <v>125.1384711218197</v>
       </c>
       <c r="D4" t="n">
-        <v>112.0056320821101</v>
+        <v>95.95013012685776</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.70602513473626</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0859965251381</v>
+        <v>205.0380080319464</v>
       </c>
       <c r="D5" t="n">
-        <v>92.65243958829274</v>
+        <v>63.64179492779949</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>13.12203981496287</v>
       </c>
       <c r="C6" t="n">
-        <v>190.7928488433252</v>
+        <v>183.1852858831166</v>
       </c>
       <c r="D6" t="n">
-        <v>58.56615929684348</v>
+        <v>36.4277485660779</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>209.1240419770216</v>
+        <v>104.9213406482651</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>154.5467236025329</v>
+        <v>49.65189014228243</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>85.75468021825461</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.02701557629594</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.800678011959</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99.45864465247725</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.775762763453876</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.904631603967817</v>
+        <v>0.414297531192154</v>
       </c>
       <c r="C2" t="n">
-        <v>11.55517047898496</v>
+        <v>5.123741268464104</v>
       </c>
       <c r="D2" t="n">
-        <v>23.74062298409637</v>
+        <v>15.5597193646077</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.36926030998382</v>
+        <v>4.025165587411922</v>
       </c>
       <c r="C3" t="n">
-        <v>24.852943133008</v>
+        <v>38.6612245932394</v>
       </c>
       <c r="D3" t="n">
-        <v>79.51665530547041</v>
+        <v>69.99370257427636</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.10350978176919</v>
+        <v>14.00070401026376</v>
       </c>
       <c r="C4" t="n">
-        <v>60.30385273336033</v>
+        <v>117.2893982263664</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9650616310665</v>
+        <v>104.6925934331756</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.44233591292137</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C5" t="n">
-        <v>114.2263453891164</v>
+        <v>242.1235275598697</v>
       </c>
       <c r="D5" t="n">
-        <v>105.4397034361075</v>
+        <v>70.34222300928397</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.82525857530663</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>189.0217759848639</v>
+        <v>220.6595775019216</v>
       </c>
       <c r="D6" t="n">
-        <v>70.3196428120863</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.40538935305847</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>235.534036968965</v>
+        <v>94.98016339506191</v>
       </c>
       <c r="D7" t="n">
-        <v>48.26860762699867</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.86628669023996</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>205.366893512869</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>127.0234267139735</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>66.76375262730434</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.95323281751981</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106.3744889343275</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.941541021899763</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.23606141737574</v>
+        <v>0.4977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>8.041495445485625</v>
+        <v>4.227405614486766</v>
       </c>
       <c r="D2" t="n">
-        <v>19.75570905255857</v>
+        <v>21.41878966355266</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>2.734167356327367</v>
       </c>
       <c r="C3" t="n">
-        <v>39.88350048502667</v>
+        <v>28.67685044104933</v>
       </c>
       <c r="D3" t="n">
-        <v>86.81104074802421</v>
+        <v>66.96991964519617</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.86704745376596</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C4" t="n">
-        <v>88.85405772056183</v>
+        <v>107.6024936285632</v>
       </c>
       <c r="D4" t="n">
-        <v>116.8554657410893</v>
+        <v>114.1114809077195</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.4889357189107</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C5" t="n">
-        <v>112.9500733735956</v>
+        <v>231.5942834318226</v>
       </c>
       <c r="D5" t="n">
-        <v>70.34222300928397</v>
+        <v>88.3082059970006</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.43275511559037</v>
+        <v>15.25537757629119</v>
       </c>
       <c r="C6" t="n">
-        <v>155.1298817388555</v>
+        <v>300.7603726914189</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>48.18123208132072</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>144.3866166112826</v>
+        <v>192.8348840681585</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>50.9203081761693</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>27.72062817711293</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.669772918474577</v>
+        <v>0.3180862561759665</v>
       </c>
       <c r="C2" t="n">
-        <v>3.963315482044373</v>
+        <v>3.22896819926776</v>
       </c>
       <c r="D2" t="n">
-        <v>14.48372388075319</v>
+        <v>15.0668820170758</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43998720241859</v>
+        <v>2.316924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>36.37375244234433</v>
+        <v>23.36068662255285</v>
       </c>
       <c r="D3" t="n">
-        <v>83.47800729210628</v>
+        <v>68.99722865446584</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.22288209105981</v>
+        <v>9.074294030353268</v>
       </c>
       <c r="C4" t="n">
-        <v>97.11153766098174</v>
+        <v>93.4613996965921</v>
       </c>
       <c r="D4" t="n">
-        <v>131.2135259156989</v>
+        <v>119.7908913767873</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.55689729468198</v>
+        <v>19.41406085148068</v>
       </c>
       <c r="C5" t="n">
-        <v>138.819125380499</v>
+        <v>226.1946710584652</v>
       </c>
       <c r="D5" t="n">
-        <v>87.3264582927538</v>
+        <v>102.4208292455485</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>18.11324514335366</v>
       </c>
       <c r="C6" t="n">
-        <v>172.9613652910903</v>
+        <v>342.0585716182652</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52712606838509</v>
+        <v>56.87558975013048</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.61233283000952</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>179.0609637775758</v>
+        <v>270.8671368448077</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>122.8362727553609</v>
+        <v>116.3272854762046</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>44.81874619427537</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.472842540548468</v>
+        <v>0.7009678608322226</v>
       </c>
       <c r="C2" t="n">
-        <v>5.931719629059228</v>
+        <v>9.137125883425064</v>
       </c>
       <c r="D2" t="n">
-        <v>17.9905266803228</v>
+        <v>18.24283584031423</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>1.722967220953152</v>
       </c>
       <c r="C3" t="n">
-        <v>25.38308689330128</v>
+        <v>18.17705874412969</v>
       </c>
       <c r="D3" t="n">
-        <v>76.36033643631691</v>
+        <v>65.28131359389165</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.72361447795468</v>
+        <v>6.917394324123026</v>
       </c>
       <c r="C4" t="n">
-        <v>94.80148531288899</v>
+        <v>77.06130429714914</v>
       </c>
       <c r="D4" t="n">
-        <v>141.2194985173824</v>
+        <v>125.2916237636822</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.85204350076177</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>157.5459628390069</v>
+        <v>201.8473279931443</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0048302608551</v>
+        <v>117.7115497391926</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.57617239586842</v>
+        <v>21.29312595740907</v>
       </c>
       <c r="C6" t="n">
-        <v>194.9387693983594</v>
+        <v>354.0133134128787</v>
       </c>
       <c r="D6" t="n">
-        <v>53.89696721544566</v>
+        <v>71.04417261782045</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>213.6754243339098</v>
+        <v>361.7151241526948</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>44.0765449298648</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>173.572994110836</v>
+        <v>212.0427779017473</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>94.62967946464578</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.644828315240907</v>
+        <v>0.4928373475318988</v>
       </c>
       <c r="C2" t="n">
-        <v>2.845104846907257</v>
+        <v>5.116869034534376</v>
       </c>
       <c r="D2" t="n">
-        <v>12.55557138961246</v>
+        <v>13.42638160327938</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35239067256238</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C3" t="n">
-        <v>26.05067533218912</v>
+        <v>26.31574721233575</v>
       </c>
       <c r="D3" t="n">
-        <v>76.06090338652164</v>
+        <v>71.74121348783568</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.76114187489431</v>
+        <v>11.79275342341269</v>
       </c>
       <c r="C4" t="n">
-        <v>93.70389137954106</v>
+        <v>110.652783745658</v>
       </c>
       <c r="D4" t="n">
-        <v>149.1961986143878</v>
+        <v>125.955285211753</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.52101459798135</v>
+        <v>12.64000169217769</v>
       </c>
       <c r="C5" t="n">
-        <v>188.3482970597506</v>
+        <v>300.8074965812227</v>
       </c>
       <c r="D5" t="n">
-        <v>115.895316486336</v>
+        <v>107.108674533327</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.37112599440108</v>
+        <v>7.486807992586177</v>
       </c>
       <c r="C6" t="n">
-        <v>235.4319352077234</v>
+        <v>311.1050482510676</v>
       </c>
       <c r="D6" t="n">
-        <v>52.56866257159972</v>
+        <v>60.0554705641859</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>223.616601587113</v>
+        <v>149.117658798048</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>120.7500588838364</v>
+        <v>60.24985660962675</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="D10" t="n">
-        <v>22.776546738526</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.703733177495716</v>
+        <v>0.2532909076956771</v>
       </c>
       <c r="C2" t="n">
-        <v>4.039891802975625</v>
+        <v>2.666426764734337</v>
       </c>
       <c r="D2" t="n">
-        <v>11.70635962543897</v>
+        <v>9.807659565425636</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.39594742444773</v>
+        <v>2.145118733779281</v>
       </c>
       <c r="C3" t="n">
-        <v>18.57957530287089</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="D3" t="n">
-        <v>69.87098411124549</v>
+        <v>66.07162049581034</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.40829353844221</v>
+        <v>8.014988257470959</v>
       </c>
       <c r="C4" t="n">
-        <v>79.77976369020855</v>
+        <v>84.82103815151592</v>
       </c>
       <c r="D4" t="n">
-        <v>152.1188615299305</v>
+        <v>126.3381668164093</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.78594760940775</v>
+        <v>11.78097245096173</v>
       </c>
       <c r="C5" t="n">
-        <v>182.6296166825129</v>
+        <v>231.9869825135214</v>
       </c>
       <c r="D5" t="n">
-        <v>136.9783484350363</v>
+        <v>112.8273549105647</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.86422538384024</v>
+        <v>7.124543089719105</v>
       </c>
       <c r="C6" t="n">
-        <v>268.2370347451306</v>
+        <v>313.4396442917665</v>
       </c>
       <c r="D6" t="n">
-        <v>70.84291433844986</v>
+        <v>63.07434475474484</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>274.1010137825967</v>
+        <v>195.4698949063569</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>190.3461536378928</v>
+        <v>71.8492057353028</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.830959468420301</v>
+        <v>0.1413716694115407</v>
       </c>
       <c r="C2" t="n">
-        <v>4.006512381031233</v>
+        <v>10.42223362828414</v>
       </c>
       <c r="D2" t="n">
-        <v>9.744827712353841</v>
+        <v>9.260826094160162</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.77606371244049</v>
+        <v>1.457895340806513</v>
       </c>
       <c r="C3" t="n">
-        <v>17.63218876827272</v>
+        <v>16.03194001035041</v>
       </c>
       <c r="D3" t="n">
-        <v>65.37948836431633</v>
+        <v>59.4644584462293</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>6.087817514034471</v>
       </c>
       <c r="C4" t="n">
-        <v>67.25953521794898</v>
+        <v>70.10562181256049</v>
       </c>
       <c r="D4" t="n">
-        <v>152.6293703361389</v>
+        <v>129.1332025304</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.98291904506286</v>
+        <v>12.14912784005428</v>
       </c>
       <c r="C5" t="n">
-        <v>175.4628584415112</v>
+        <v>192.7661617288613</v>
       </c>
       <c r="D5" t="n">
-        <v>150.5510104462484</v>
+        <v>131.8732603729528</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.90197376495812</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>288.8861342085538</v>
+        <v>345.3994590558171</v>
       </c>
       <c r="D6" t="n">
-        <v>85.33351045313277</v>
+        <v>82.11337798320324</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>322.1899615797182</v>
+        <v>320.0939302311513</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>237.9952784635118</v>
+        <v>160.8888137719673</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>85.53280523709483</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.54861704022472</v>
+        <v>0.04319689898685965</v>
       </c>
       <c r="C2" t="n">
-        <v>6.663121668723102</v>
+        <v>16.47274472955723</v>
       </c>
       <c r="D2" t="n">
-        <v>14.34038871593316</v>
+        <v>14.87347771933918</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.154797342101507</v>
+        <v>0.9621127501618741</v>
       </c>
       <c r="C3" t="n">
-        <v>16.69952844923824</v>
+        <v>28.27433388230814</v>
       </c>
       <c r="D3" t="n">
-        <v>59.19447782756144</v>
+        <v>53.67705572969436</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.08249216935251</v>
+        <v>4.479714774478196</v>
       </c>
       <c r="C4" t="n">
-        <v>57.01107093331653</v>
+        <v>54.59891682398212</v>
       </c>
       <c r="D4" t="n">
-        <v>150.4852333500639</v>
+        <v>129.3629314931937</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.03200643027521</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>153.6435157146258</v>
+        <v>162.0374585859361</v>
       </c>
       <c r="D5" t="n">
-        <v>165.1790512395259</v>
+        <v>144.4641746799182</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.67054334866313</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>286.0685182973654</v>
+        <v>329.137790082673</v>
       </c>
       <c r="D6" t="n">
-        <v>104.3725436815912</v>
+        <v>101.5951794262769</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>361.0563714431452</v>
+        <v>403.5159779041155</v>
       </c>
       <c r="D7" t="n">
-        <v>52.70021676396878</v>
+        <v>52.99964981376406</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>312.5148379543659</v>
+        <v>276.548510809284</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>157.8640490951828</v>
+        <v>119.3687398639611</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>54.8060655895782</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.458116324984766</v>
+        <v>2.767546778271758</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98517597344506</v>
+        <v>15.51455897021235</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2792993740916</v>
+        <v>10.42616061910113</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.842740440871263</v>
+        <v>0.2208932334555323</v>
       </c>
       <c r="C2" t="n">
-        <v>3.837651775900782</v>
+        <v>14.467034169781</v>
       </c>
       <c r="D2" t="n">
-        <v>10.66865230205009</v>
+        <v>15.64611316258142</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18839774822415</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C3" t="n">
-        <v>21.88806506618264</v>
+        <v>44.18846416814893</v>
       </c>
       <c r="D3" t="n">
-        <v>64.72662614099221</v>
+        <v>52.71985171805372</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.92254940901829</v>
+        <v>3.267256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>84.20842758406592</v>
+        <v>60.91646330081034</v>
       </c>
       <c r="D4" t="n">
-        <v>154.964948124542</v>
+        <v>126.8869637830833</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.86338250485623</v>
+        <v>9.179341034707679</v>
       </c>
       <c r="C5" t="n">
-        <v>237.263876423848</v>
+        <v>135.1130277969673</v>
       </c>
       <c r="D5" t="n">
-        <v>150.1092239793373</v>
+        <v>152.6863117029852</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.6981457909065</v>
+        <v>13.96732458831938</v>
       </c>
       <c r="C6" t="n">
-        <v>291.0597236257562</v>
+        <v>298.103763403727</v>
       </c>
       <c r="D6" t="n">
-        <v>81.30834486572085</v>
+        <v>118.4606232375329</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.491495746929157</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>219.7838585497334</v>
+        <v>437.1123660911456</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>64.43799231594365</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>116.3272854762046</v>
+        <v>380.1081673917588</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>209.3390447242516</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>79.71791358484101</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.297510612115789</v>
+        <v>4.372704274715294</v>
       </c>
       <c r="C2" t="n">
-        <v>11.26751840164064</v>
+        <v>13.05626271877833</v>
       </c>
       <c r="D2" t="n">
-        <v>18.70327551360598</v>
+        <v>17.93751230429347</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.47386534598172</v>
+        <v>4.476769531365455</v>
       </c>
       <c r="C3" t="n">
-        <v>30.19855938263188</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61054926105028</v>
+        <v>10.14145378486955</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39724346825993</v>
+        <v>11.67746202682037</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13850992206669</v>
+        <v>59.94430507101124</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576146290383521</v>
+        <v>0.7784974684546915</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.900884539600077</v>
+        <v>2.941316121923444</v>
       </c>
       <c r="C2" t="n">
-        <v>7.196210672129119</v>
+        <v>9.52884321741954</v>
       </c>
       <c r="D2" t="n">
-        <v>31.47581314585699</v>
+        <v>21.96660488252238</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7605767333508</v>
+        <v>11.19683256693487</v>
       </c>
       <c r="C3" t="n">
-        <v>38.79866927183394</v>
+        <v>44.53207586463532</v>
       </c>
       <c r="D3" t="n">
-        <v>25.2701859073129</v>
+        <v>23.37541283811656</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.12909197534184</v>
+        <v>5.730461349688633</v>
       </c>
       <c r="C4" t="n">
-        <v>46.55840312620073</v>
+        <v>49.54487964251953</v>
       </c>
       <c r="D4" t="n">
-        <v>21.6838615436993</v>
+        <v>19.55248727777947</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.436750114463</v>
+        <v>13.62593760560523</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12081642805673</v>
+        <v>73.7403682185695</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249842129360631</v>
+        <v>1.60305148301238</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.602834148136546</v>
+        <v>1.622828955119977</v>
       </c>
       <c r="C2" t="n">
-        <v>11.90172741858408</v>
+        <v>4.944081438586937</v>
       </c>
       <c r="D2" t="n">
-        <v>30.11609257547515</v>
+        <v>27.3613085173586</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94849145548944</v>
+        <v>10.67159754516283</v>
       </c>
       <c r="C3" t="n">
-        <v>32.33876937788994</v>
+        <v>40.30074325933157</v>
       </c>
       <c r="D3" t="n">
-        <v>44.5860719883689</v>
+        <v>36.17740290149496</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.71389481190345</v>
+        <v>15.13658610407732</v>
       </c>
       <c r="C4" t="n">
-        <v>75.8233204420939</v>
+        <v>87.29700586162639</v>
       </c>
       <c r="D4" t="n">
-        <v>29.46912083837651</v>
+        <v>27.26117025152543</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.11200135374215</v>
+        <v>5.767767762450012</v>
       </c>
       <c r="C5" t="n">
-        <v>50.56000676871075</v>
+        <v>56.03325021988672</v>
       </c>
       <c r="D5" t="n">
-        <v>30.72870314292517</v>
+        <v>27.21895510024282</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72107527038823</v>
+        <v>14.82987168812254</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1625053858488</v>
+        <v>87.33146660783274</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180268817597057</v>
+        <v>2.471645281353756</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.636213570080939</v>
+        <v>1.198713946885355</v>
       </c>
       <c r="C2" t="n">
-        <v>7.714573459971436</v>
+        <v>7.493680226515903</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53529884518854</v>
+        <v>29.09507496305847</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>7.839255418410781</v>
       </c>
       <c r="C3" t="n">
-        <v>40.46273163053229</v>
+        <v>27.71473769088746</v>
       </c>
       <c r="D3" t="n">
-        <v>56.77937847511428</v>
+        <v>49.67152509636737</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.78069471352124</v>
+        <v>18.17411350101695</v>
       </c>
       <c r="C4" t="n">
-        <v>77.78877934599602</v>
+        <v>95.20989235785567</v>
       </c>
       <c r="D4" t="n">
-        <v>43.22733316569131</v>
+        <v>39.24536447726624</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.24854640009047</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C5" t="n">
-        <v>97.95387719122553</v>
+        <v>114.9871998599077</v>
       </c>
       <c r="D5" t="n">
-        <v>34.26299487821369</v>
+        <v>30.97414006898687</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781152377410974</v>
+        <v>6.279258316362601</v>
       </c>
       <c r="C6" t="n">
-        <v>46.61141750223008</v>
+        <v>52.60891422747383</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03034071150518</v>
+        <v>16.05999493872477</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7679207983193</v>
+        <v>100.5862840899077</v>
       </c>
       <c r="D21" t="n">
-        <v>6.010113570501727</v>
+        <v>3.381051566047319</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.348561492736622</v>
+        <v>1.3695380474243</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>11.15658091106075</v>
       </c>
       <c r="D2" t="n">
-        <v>25.80327491071892</v>
+        <v>25.7777494704085</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.30192062901829</v>
+        <v>5.82667262470482</v>
       </c>
       <c r="C3" t="n">
-        <v>32.43694414831462</v>
+        <v>28.42159603794516</v>
       </c>
       <c r="D3" t="n">
-        <v>62.66495596207391</v>
+        <v>60.04859833025616</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.64557338323367</v>
+        <v>16.47667172037422</v>
       </c>
       <c r="C4" t="n">
-        <v>75.46596427774806</v>
+        <v>81.22195106774711</v>
       </c>
       <c r="D4" t="n">
-        <v>51.8932201510779</v>
+        <v>53.20778032706438</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.76963344686727</v>
+        <v>20.91122610045706</v>
       </c>
       <c r="C5" t="n">
-        <v>89.43721585688444</v>
+        <v>145.4704660767711</v>
       </c>
       <c r="D5" t="n">
-        <v>33.72303364087794</v>
+        <v>37.69911184307752</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.02266231265569</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>68.50831829775093</v>
+        <v>118.6216298610294</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>27.78738702100172</v>
+        <v>46.77144237802229</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.038716853856241</v>
+        <v>17.30952485115004</v>
       </c>
       <c r="C21" t="n">
-        <v>65.98797050490226</v>
+        <v>113.3773877750328</v>
       </c>
       <c r="D21" t="n">
-        <v>4.39919803366015</v>
+        <v>4.327381212787511</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.262748531839651</v>
+        <v>1.334195130071415</v>
       </c>
       <c r="C2" t="n">
-        <v>3.975096454495335</v>
+        <v>13.97714206536184</v>
       </c>
       <c r="D2" t="n">
-        <v>24.01354884587698</v>
+        <v>23.94286301117121</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.71563732313369</v>
+        <v>5.178719139901925</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55841882173396</v>
+        <v>36.39829613495049</v>
       </c>
       <c r="D3" t="n">
-        <v>69.19848693383643</v>
+        <v>65.37457962579511</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.8099672181994</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C4" t="n">
-        <v>79.0905768018273</v>
+        <v>75.23623531495431</v>
       </c>
       <c r="D4" t="n">
-        <v>72.69645400406782</v>
+        <v>67.87214578539898</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.89359569950963</v>
+        <v>22.85017781634452</v>
       </c>
       <c r="C5" t="n">
-        <v>119.1105402177443</v>
+        <v>147.4830488704771</v>
       </c>
       <c r="D5" t="n">
-        <v>45.38128762880881</v>
+        <v>47.09934611124073</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.91198686398306</v>
+        <v>19.60255641069606</v>
       </c>
       <c r="C6" t="n">
-        <v>109.7662655687232</v>
+        <v>170.3852593151467</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>68.45039518320036</v>
+        <v>105.2207736980604</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>42.30841731451629</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.251261286679978</v>
+        <v>17.68811504731321</v>
       </c>
       <c r="C21" t="n">
-        <v>75.23183584930477</v>
+        <v>125.5856168359238</v>
       </c>
       <c r="D21" t="n">
-        <v>5.438445965009984</v>
+        <v>5.306434514193963</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.505240214788612</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C2" t="n">
-        <v>7.560439070404686</v>
+        <v>8.94470333339269</v>
       </c>
       <c r="D2" t="n">
-        <v>22.85999529338698</v>
+        <v>19.14702547592554</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.01230505626548</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27661617288612</v>
+        <v>56.67629496616836</v>
       </c>
       <c r="D3" t="n">
-        <v>72.05537275319465</v>
+        <v>70.30786183963532</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47286790274425</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>68.484756352849</v>
+        <v>118.3997548798696</v>
       </c>
       <c r="D4" t="n">
-        <v>90.04099069499621</v>
+        <v>62.06510811477911</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C5" t="n">
-        <v>134.0331053222958</v>
+        <v>101.8072369303943</v>
       </c>
       <c r="D5" t="n">
-        <v>59.86206626644928</v>
+        <v>36.71736413883072</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.84785446803753</v>
+        <v>6.681774875103793</v>
       </c>
       <c r="C6" t="n">
-        <v>152.0707558924225</v>
+        <v>69.2730997593592</v>
       </c>
       <c r="D6" t="n">
-        <v>40.77492740048278</v>
+        <v>25.318291544821</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.15131231964102</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>115.1619509512636</v>
+        <v>29.70375853969149</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58503348740241</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.34153469455343</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.449546870891117</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.80740229752507</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.518353512029727</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
